--- a/output/pdf_financials_xlsx/MONY.P.xlsx
+++ b/output/pdf_financials_xlsx/MONY.P.xlsx
@@ -2633,10 +2633,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.010446</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.010446</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0.010446</v>
@@ -3995,7 +3995,11 @@
           <t>Warrants reserve (note 4)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -4315,7 +4319,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MONY.P.xlsx
+++ b/output/pdf_financials_xlsx/MONY.P.xlsx
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.022262</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.150371</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.064835</v>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.209739</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.243964</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.177369</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.117953</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.072031</v>
       </c>
     </row>
     <row r="35">
@@ -1338,19 +1338,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.209739</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.243964</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.177369</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.117953</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.072031</v>
       </c>
     </row>
     <row r="37">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
